--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file AR CCPC STATEMENTS (349.2) to ChargeItem</t>
+    <t>This StructureDefinition contains the maps for VistA file INTEGRATED BILLING ACTION (350) to ChargeItem</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -490,7 +490,10 @@
     <t>Allows identification of the charge Item as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t>1837: source value from AR CCPC STATEMENTS - PD LINE &gt; PD LINE - BILL REF. NO. (349.2-20 &gt; 349.21-3)</t>
+    <t>1837: source value from INTEGRATED BILLING ACTION - AR BILL NUMBER (350-.11)</t>
+  </si>
+  <si>
+    <t>IB.IBAction.ARBillNumber</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -721,7 +724,11 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1836: source value from AR CCPC STATEMENTS - PD LINE &gt; PD LINE - TRANSACTION DESCRIPTION (349.2-20 &gt; 349.21-1)</t>
+    <t>1836: source value from INTEGRATED BILLING ACTION - ACTION TYPE &gt; IB ACTION TYPES - NAME (350-.03 &gt; 350.1-.01)</t>
+  </si>
+  <si>
+    <t>IB.IBAction.IBActionTypeIEN
+Dim.IBActionType.IBActionType</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -750,10 +757,10 @@
     <t>Links the event to the Patient context.</t>
   </si>
   <si>
-    <t>1839: reference from AR CCPC STATEMENTS - PATIENT &gt; AR DEBTOR - DEBTOR (349.2-.01 &gt; 340-.01)</t>
-  </si>
-  <si>
-    <t>Dim.ARDebtor.InstitutionIEN,Dim.ARDebtor.InsuranceCompanyIEN,Dim.ARDebtor.PatientIEN,Dim.ARDebtor.StaffIEN,Dim.ARDebtor.VendorIEN</t>
+    <t>1839: reference from INTEGRATED BILLING ACTION - PATIENT (350-.02)</t>
+  </si>
+  <si>
+    <t>IB.IBAction.PatientIEN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -820,6 +827,10 @@
     <t>The list of types may be constrained as appropriate for the type of charge item.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -827,6 +838,99 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x]:occurrencePeriod</t>
+  </si>
+  <si>
+    <t>occurrencePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x]:occurrencePeriod.id</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x].id</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x]:occurrencePeriod.extension</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x].extension</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x]:occurrencePeriod.start</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>1840: source value from INTEGRATED BILLING ACTION - DATE BILLED FROM (350-.14)</t>
+  </si>
+  <si>
+    <t>IB.IBAction.BillFromDateTime</t>
+  </si>
+  <si>
+    <t>DR.1</t>
+  </si>
+  <si>
+    <t>./low</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x]:occurrencePeriod.end</t>
+  </si>
+  <si>
+    <t>ChargeItem.occurrence[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
+  </si>
+  <si>
+    <t>1841: source value from INTEGRATED BILLING ACTION - DATE BILLED TO (350-.15)</t>
+  </si>
+  <si>
+    <t>IB.IBAction.BillToDateTime</t>
+  </si>
+  <si>
+    <t>DR.2</t>
+  </si>
+  <si>
+    <t>./high</t>
   </si>
   <si>
     <t>ChargeItem.performer</t>
@@ -1072,10 +1176,6 @@
     <t>ChargeItem.enteredDate</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
     <t>Date the charge item was entered</t>
   </si>
   <si>
@@ -1085,7 +1185,10 @@
     <t>The actual date when the service associated with the charge has been rendered is captured in occurrence[x].</t>
   </si>
   <si>
-    <t>1835: source value from AR CCPC STATEMENTS - PD LINE &gt; PD LINE - DATE POSTED (349.2-20 &gt; 349.21-.01)</t>
+    <t>1835: source value from INTEGRATED BILLING ACTION - DATE ENTRY ADDED (350-12)</t>
+  </si>
+  <si>
+    <t>IB.IBAction.EnteredDateTime</t>
   </si>
   <si>
     <t>ChargeItem.reason</t>
@@ -1527,12 +1630,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP45"/>
+  <dimension ref="A1:AP50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.84375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.34375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.84375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.05859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1565,8 +1668,8 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="113.078125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="131.55859375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="111.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="97.8125" customWidth="true" bestFit="true"/>
@@ -2884,27 +2987,27 @@
         <v>152</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2930,10 +3033,10 @@
         <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2984,7 +3087,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3005,13 +3108,13 @@
         <v>79</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>79</v>
@@ -3019,10 +3122,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3045,13 +3148,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3102,7 +3205,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3123,13 +3226,13 @@
         <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>79</v>
@@ -3137,10 +3240,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3166,13 +3269,13 @@
         <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3183,7 +3286,7 @@
         <v>79</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>79</v>
@@ -3198,13 +3301,13 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3222,7 +3325,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3237,34 +3340,34 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3283,17 +3386,17 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3342,7 +3445,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3363,13 +3466,13 @@
         <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>79</v>
@@ -3377,14 +3480,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3403,13 +3506,13 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3436,13 +3539,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3460,7 +3563,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>90</v>
@@ -3481,24 +3584,24 @@
         <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3521,13 +3624,13 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3578,7 +3681,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3605,7 +3708,7 @@
         <v>79</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3613,10 +3716,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3645,7 +3748,7 @@
         <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>139</v>
@@ -3686,19 +3789,19 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3725,7 +3828,7 @@
         <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -3733,10 +3836,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3759,19 +3862,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3820,7 +3923,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3844,10 +3947,10 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -3855,10 +3958,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3881,19 +3984,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3942,7 +4045,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3957,19 +4060,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -3977,14 +4080,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4003,17 +4106,17 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4062,7 +4165,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>90</v>
@@ -4077,34 +4180,34 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4123,17 +4226,17 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4182,7 +4285,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4203,28 +4306,28 @@
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4243,16 +4346,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4290,19 +4393,17 @@
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4323,35 +4424,37 @@
         <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>254</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>79</v>
@@ -4360,18 +4463,20 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4420,13 +4525,13 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
@@ -4441,21 +4546,21 @@
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>265</v>
+        <v>162</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>267</v>
@@ -4481,13 +4586,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4538,7 +4643,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4565,7 +4670,7 @@
         <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -4576,7 +4681,7 @@
         <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4605,7 +4710,7 @@
         <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>139</v>
@@ -4646,19 +4751,19 @@
         <v>79</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4685,7 +4790,7 @@
         <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -4693,46 +4798,44 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>136</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -4780,34 +4883,34 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>133</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -4815,10 +4918,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4832,29 +4935,33 @@
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="R28" t="s" s="2">
         <v>79</v>
       </c>
@@ -4874,13 +4981,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4898,7 +5005,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4907,25 +5014,25 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>161</v>
+        <v>291</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -4933,10 +5040,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4944,10 +5051,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -4959,13 +5066,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5016,13 +5123,13 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
@@ -5037,24 +5144,24 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5077,17 +5184,15 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>289</v>
+        <v>201</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>290</v>
+        <v>202</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5136,7 +5241,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5148,7 +5253,7 @@
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>79</v>
@@ -5157,13 +5262,13 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>293</v>
+        <v>205</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5171,21 +5276,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5197,16 +5302,16 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>289</v>
+        <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>207</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>297</v>
+        <v>139</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5256,19 +5361,19 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>211</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -5280,10 +5385,10 @@
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>293</v>
+        <v>205</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5291,44 +5396,46 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>289</v>
+        <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5376,19 +5483,19 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>79</v>
@@ -5400,10 +5507,10 @@
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>79</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5411,10 +5518,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5434,20 +5541,18 @@
         <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>304</v>
+        <v>190</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5472,13 +5577,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5496,7 +5601,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5517,13 +5622,13 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>308</v>
+        <v>162</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5531,10 +5636,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5542,10 +5647,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>79</v>
@@ -5554,20 +5659,18 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>189</v>
+        <v>315</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5592,37 +5695,37 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AA34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -5637,24 +5740,24 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5677,16 +5780,16 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5736,7 +5839,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5757,13 +5860,13 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>321</v>
+        <v>133</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -5771,10 +5874,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5797,16 +5900,16 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5856,7 +5959,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5880,10 +5983,10 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>327</v>
+        <v>133</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -5891,10 +5994,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5917,16 +6020,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>200</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5976,7 +6079,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6000,7 +6103,7 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6011,10 +6114,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6037,16 +6140,16 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6096,7 +6199,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6120,21 +6223,21 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6145,10 +6248,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>79</v>
@@ -6157,16 +6260,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>338</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6192,13 +6295,13 @@
         <v>79</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>79</v>
@@ -6216,13 +6319,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6231,7 +6334,7 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -6243,7 +6346,7 @@
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6251,10 +6354,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6265,7 +6368,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6277,16 +6380,16 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>350</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6312,13 +6415,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6336,13 +6439,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -6357,24 +6460,24 @@
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6385,7 +6488,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6397,15 +6500,17 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6454,13 +6559,13 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
@@ -6475,24 +6580,24 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6515,15 +6620,17 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>360</v>
+        <v>201</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6548,13 +6655,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6572,7 +6679,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6599,7 +6706,7 @@
         <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -6607,10 +6714,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6621,7 +6728,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
@@ -6633,16 +6740,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6692,13 +6799,13 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
@@ -6716,21 +6823,21 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6741,27 +6848,29 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6810,13 +6919,13 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
@@ -6825,19 +6934,19 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>79</v>
+        <v>375</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -6845,10 +6954,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6871,15 +6980,17 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -6904,13 +7015,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6928,7 +7039,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6952,17 +7063,609 @@
         <v>382</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AP45" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP45">
+  <autoFilter ref="A1:AP50">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6972,7 +7675,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI44">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-DebtPortalChargeItem.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargeItem.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
